--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.01868506652885</v>
+        <v>6.503036323310938</v>
       </c>
       <c r="D2" t="n">
-        <v>40.02998921610277</v>
+        <v>6.5048732476167</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2721361418391</v>
+        <v>1.344222123048854</v>
       </c>
       <c r="F2" t="n">
-        <v>8.184993047663133</v>
+        <v>1.330061370245259</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.41401416001601</v>
+        <v>6.242277301002602</v>
       </c>
       <c r="D3" t="n">
-        <v>38.39279347162192</v>
+        <v>6.238828939138562</v>
       </c>
       <c r="E3" t="n">
-        <v>8.2721361418391</v>
+        <v>1.344222123048854</v>
       </c>
       <c r="F3" t="n">
-        <v>8.184993047663133</v>
+        <v>1.330061370245259</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.29493837894576</v>
+        <v>5.247927486578686</v>
       </c>
       <c r="D4" t="n">
-        <v>31.86029700108883</v>
+        <v>5.177298262676935</v>
       </c>
       <c r="E4" t="n">
-        <v>8.2721361418391</v>
+        <v>1.344222123048854</v>
       </c>
       <c r="F4" t="n">
-        <v>8.184993047663133</v>
+        <v>1.330061370245259</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.71068991736483</v>
+        <v>4.015487111571785</v>
       </c>
       <c r="D5" t="n">
-        <v>24.68989252204452</v>
+        <v>4.012107534832234</v>
       </c>
       <c r="E5" t="n">
-        <v>8.2721361418391</v>
+        <v>1.344222123048854</v>
       </c>
       <c r="F5" t="n">
-        <v>8.184993047663133</v>
+        <v>1.330061370245259</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.81473654335526</v>
+        <v>5.65739468829523</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77844603567067</v>
+        <v>5.651497480796484</v>
       </c>
       <c r="E6" t="n">
-        <v>8.2721361418391</v>
+        <v>1.344222123048854</v>
       </c>
       <c r="F6" t="n">
-        <v>8.184993047663133</v>
+        <v>1.330061370245259</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.54083118322811</v>
+        <v>6.262885067274568</v>
       </c>
       <c r="D7" t="n">
-        <v>38.59838972684894</v>
+        <v>6.272238330612954</v>
       </c>
       <c r="E7" t="n">
-        <v>8.2721361418391</v>
+        <v>1.344222123048854</v>
       </c>
       <c r="F7" t="n">
-        <v>8.184993047663133</v>
+        <v>1.330061370245259</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>9.639795954288305</v>
+        <v>1.56646684257185</v>
       </c>
       <c r="D8" t="n">
-        <v>9.806102888858698</v>
+        <v>1.593491719439538</v>
       </c>
       <c r="E8" t="n">
-        <v>8.2721361418391</v>
+        <v>1.344222123048854</v>
       </c>
       <c r="F8" t="n">
-        <v>8.184993047663133</v>
+        <v>1.330061370245259</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.65078381880254</v>
+        <v>5.143252370555413</v>
       </c>
       <c r="D9" t="n">
-        <v>31.66048919211401</v>
+        <v>5.144829493718526</v>
       </c>
       <c r="E9" t="n">
-        <v>8.2721361418391</v>
+        <v>1.344222123048854</v>
       </c>
       <c r="F9" t="n">
-        <v>8.184993047663133</v>
+        <v>1.330061370245259</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.54274660086103</v>
+        <v>5.288196322639918</v>
       </c>
       <c r="D10" t="n">
-        <v>31.76872058846621</v>
+        <v>5.162417095625759</v>
       </c>
       <c r="E10" t="n">
-        <v>8.2721361418391</v>
+        <v>1.344222123048854</v>
       </c>
       <c r="F10" t="n">
-        <v>8.184993047663133</v>
+        <v>1.330061370245259</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.27433519493573</v>
+        <v>6.707079469177057</v>
       </c>
       <c r="D11" t="n">
-        <v>40.70891758441188</v>
+        <v>6.61519910746693</v>
       </c>
       <c r="E11" t="n">
-        <v>8.2721361418391</v>
+        <v>1.344222123048854</v>
       </c>
       <c r="F11" t="n">
-        <v>8.184993047663133</v>
+        <v>1.330061370245259</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.64417383994405</v>
+        <v>5.792178248990908</v>
       </c>
       <c r="D12" t="n">
-        <v>35.84626451017057</v>
+        <v>5.825017982902718</v>
       </c>
       <c r="E12" t="n">
-        <v>8.2721361418391</v>
+        <v>1.344222123048854</v>
       </c>
       <c r="F12" t="n">
-        <v>8.184993047663133</v>
+        <v>1.330061370245259</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>28.34655662781491</v>
+        <v>4.606315452019923</v>
       </c>
       <c r="D13" t="n">
-        <v>28.66193798899933</v>
+        <v>4.657564923212391</v>
       </c>
       <c r="E13" t="n">
-        <v>8.2721361418391</v>
+        <v>1.344222123048854</v>
       </c>
       <c r="F13" t="n">
-        <v>8.184993047663133</v>
+        <v>1.330061370245259</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
